--- a/packages/examples/showcase/territory-performance-matrix/artifact/territory-performance-matrix.xlsx
+++ b/packages/examples/showcase/territory-performance-matrix/artifact/territory-performance-matrix.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Territory Matrix" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -200,10 +201,10 @@
     <tableColumn id="5" name="EMEA" totalsRowFunction="sum"/>
     <tableColumn id="6" name="APAC" totalsRowFunction="sum"/>
     <tableColumn id="7" name="Regional Total" totalsRowFunction="sum">
-      <calculatedColumnFormula>SUM(territories[@[AMER]:[APAC]])</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(territories[[#This Row],[AMER]:[APAC]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Regional Avg" totalsRowFunction="average">
-      <calculatedColumnFormula>ROUND(AVERAGE(territories[@[AMER]:[APAC]]),0)</calculatedColumnFormula>
+      <calculatedColumnFormula>ROUND(AVERAGE(territories[[#This Row],[AMER]:[APAC]]),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -271,10 +272,12 @@
         <v>250497</v>
       </c>
       <c r="G2" s="4">
-        <f>SUM([@[AMER]],[@[EMEA]],[@[APAC]])</f>
+        <f>SUM(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]])</f>
+        <v>760182</v>
       </c>
       <c r="H2" s="3">
-        <f>ROUND(AVERAGE([@[AMER]],[@[EMEA]],[@[APAC]]),0)</f>
+        <f>ROUND(AVERAGE(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]]),0)</f>
+        <v>253394</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
@@ -297,10 +300,12 @@
         <v>294759</v>
       </c>
       <c r="G3" s="4">
-        <f>SUM([@[AMER]],[@[EMEA]],[@[APAC]])</f>
+        <f>SUM(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]])</f>
+        <v>741335</v>
       </c>
       <c r="H3" s="3">
-        <f>ROUND(AVERAGE([@[AMER]],[@[EMEA]],[@[APAC]]),0)</f>
+        <f>ROUND(AVERAGE(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]]),0)</f>
+        <v>247112</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -323,10 +328,12 @@
         <v>287828</v>
       </c>
       <c r="G4" s="4">
-        <f>SUM([@[AMER]],[@[EMEA]],[@[APAC]])</f>
+        <f>SUM(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]])</f>
+        <v>958751</v>
       </c>
       <c r="H4" s="3">
-        <f>ROUND(AVERAGE([@[AMER]],[@[EMEA]],[@[APAC]]),0)</f>
+        <f>ROUND(AVERAGE(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]]),0)</f>
+        <v>319584</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -349,10 +356,12 @@
         <v>273913</v>
       </c>
       <c r="G5" s="4">
-        <f>SUM([@[AMER]],[@[EMEA]],[@[APAC]])</f>
+        <f>SUM(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]])</f>
+        <v>1088635</v>
       </c>
       <c r="H5" s="3">
-        <f>ROUND(AVERAGE([@[AMER]],[@[EMEA]],[@[APAC]]),0)</f>
+        <f>ROUND(AVERAGE(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]]),0)</f>
+        <v>362878</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -375,10 +384,12 @@
         <v>198590</v>
       </c>
       <c r="G6" s="4">
-        <f>SUM([@[AMER]],[@[EMEA]],[@[APAC]])</f>
+        <f>SUM(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]])</f>
+        <v>758817</v>
       </c>
       <c r="H6" s="3">
-        <f>ROUND(AVERAGE([@[AMER]],[@[EMEA]],[@[APAC]]),0)</f>
+        <f>ROUND(AVERAGE(territories[[#This Row],[AMER]],territories[[#This Row],[EMEA]],territories[[#This Row],[APAC]]),0)</f>
+        <v>252939</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -387,18 +398,23 @@
       </c>
       <c r="D7" s="6">
         <f>SUBTOTAL(109,[AMER])</f>
+        <v>1602135</v>
       </c>
       <c r="E7" s="6">
         <f>SUBTOTAL(109,[EMEA])</f>
+        <v>1399998</v>
       </c>
       <c r="F7" s="6">
         <f>SUBTOTAL(109,[APAC])</f>
+        <v>1305587</v>
       </c>
       <c r="G7" s="6">
         <f>SUBTOTAL(109,[Regional Total])</f>
+        <v>4307720</v>
       </c>
       <c r="H7" s="6">
         <f>SUBTOTAL(101,[Regional Avg])</f>
+        <v>287181.4</v>
       </c>
     </row>
   </sheetData>
